--- a/data/trans_bre/IMC_inf_MED_R3-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IMC_inf_MED_R3-Provincia-trans_bre.xlsx
@@ -604,19 +604,19 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>-6.268605759094911</v>
+        <v>-6.793469519756664</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>-4.810743456615047</v>
+        <v>-8.356276269090532</v>
       </c>
       <c r="E4" s="5" t="n">
         <v>-5.07903180054476</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>-0.2223390703710995</v>
+        <v>-0.2559203716973451</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>-0.1663319692065418</v>
+        <v>-0.333833624109627</v>
       </c>
       <c r="H4" s="6" t="n">
         <v>-0.4859309985875375</v>
@@ -630,19 +630,19 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>-23.94985522068061</v>
+        <v>-21.2129567793076</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>-21.71876652754198</v>
+        <v>-20.89429184514283</v>
       </c>
       <c r="E5" s="5" t="n">
         <v>-17.86904783213538</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>-0.6695368434086986</v>
+        <v>-0.6190714132589566</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>-0.6008895351009462</v>
+        <v>-0.6777480906031907</v>
       </c>
       <c r="H5" s="6" t="inlineStr"/>
     </row>
@@ -654,19 +654,19 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>11.69760236193713</v>
+        <v>7.864820898500033</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>13.61335351429114</v>
+        <v>4.569637517657411</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>5.750644879698967</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0.6223610414666544</v>
+        <v>0.4440491464950106</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.8257293640213863</v>
+        <v>0.2839774036480144</v>
       </c>
       <c r="H6" s="6" t="inlineStr"/>
     </row>
@@ -682,22 +682,22 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>-3.723338836368284</v>
+        <v>-1.09902107909905</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>-12.13567307970495</v>
+        <v>-11.19013226749533</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>-1.956750246914032</v>
+        <v>-1.588000283289046</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>-0.1222293832283199</v>
+        <v>-0.03852812958847487</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>-0.4079939013122039</v>
+        <v>-0.4114737991261506</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>-0.1202631781719037</v>
+        <v>-0.09986281165658334</v>
       </c>
     </row>
     <row r="8">
@@ -708,22 +708,22 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>-16.23839093270298</v>
+        <v>-13.59218260792364</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>-22.73874029742916</v>
+        <v>-20.79342341133691</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>-18.80713601006891</v>
+        <v>-18.37520749110421</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>-0.4375148901878432</v>
+        <v>-0.3885867163285097</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>-0.6566586160501662</v>
+        <v>-0.6491325806191868</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>-0.7256885516000914</v>
+        <v>-0.7310671110645758</v>
       </c>
     </row>
     <row r="9">
@@ -734,22 +734,22 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>7.409529988218523</v>
+        <v>9.541637327351664</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>-0.5273141381287859</v>
+        <v>-1.919062732928412</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>12.33899693100938</v>
+        <v>11.54979668624064</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>0.3128778122085291</v>
+        <v>0.3772209172231413</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>-0.01628155316962848</v>
+        <v>-0.06217636340336101</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>1.571300760173492</v>
+        <v>1.359232723386307</v>
       </c>
     </row>
     <row r="10">
@@ -764,22 +764,22 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>-0.922475266480044</v>
+        <v>-1.995805600525896</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>-12.55141016579564</v>
+        <v>-11.93915007687271</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>-17.01161676305081</v>
+        <v>-16.57910476820141</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>-0.0468202301656189</v>
+        <v>-0.1026130799275125</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>-0.5741759611786207</v>
+        <v>-0.5652175420375528</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>-0.5154927869680352</v>
+        <v>-0.5232832047380779</v>
       </c>
     </row>
     <row r="11">
@@ -790,22 +790,22 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>-13.91091139785893</v>
+        <v>-13.1581736423536</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>-24.66828312733967</v>
+        <v>-22.18346534538727</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>-34.6304180635035</v>
+        <v>-34.87657084240263</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>-0.5510844178596217</v>
+        <v>-0.5379810471440606</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>-0.8580165930708341</v>
+        <v>-0.829156617886904</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>-0.8196246559569912</v>
+        <v>-0.8376873509399251</v>
       </c>
     </row>
     <row r="12">
@@ -816,22 +816,22 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>11.51127466536269</v>
+        <v>9.471489861639732</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>-1.564731847358768</v>
+        <v>-1.146806451471382</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>2.520777610828044</v>
+        <v>1.09398211142408</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>0.8948322758370711</v>
+        <v>0.7020208439529158</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>-0.07197518999479226</v>
+        <v>-0.03704106361175138</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.1614219294517565</v>
+        <v>0.132506169118524</v>
       </c>
     </row>
     <row r="13">
@@ -846,22 +846,22 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>-14.4464642841015</v>
+        <v>-12.87092693664809</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>-12.65622654126375</v>
+        <v>-13.24821062244687</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>-6.293158683283245</v>
+        <v>-4.099766223939051</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>-0.5059057573721898</v>
+        <v>-0.5010305075282435</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>-0.4520393693341849</v>
+        <v>-0.5235376685935461</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>-0.5583447314279937</v>
+        <v>-0.4583232475842631</v>
       </c>
     </row>
     <row r="14">
@@ -872,19 +872,19 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>-26.58411732506809</v>
+        <v>-25.146437112517</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>-27.019120069111</v>
+        <v>-26.67528691746968</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>-29.76513018102644</v>
+        <v>-22.04395666506555</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>-0.7707844219308423</v>
+        <v>-0.7572757413287466</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>-0.7618127558088268</v>
+        <v>-0.7895850961400995</v>
       </c>
       <c r="H14" s="6" t="inlineStr"/>
     </row>
@@ -896,19 +896,19 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>-0.1767313466378872</v>
+        <v>-1.317678839543129</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>2.983767088238888</v>
+        <v>-0.8921635392803174</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>8.860801172703644</v>
+        <v>9.684591702398643</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>0.02911568327720516</v>
+        <v>0.01635340787924631</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>0.2051024778792994</v>
+        <v>-0.01452596024488838</v>
       </c>
       <c r="H15" s="6" t="inlineStr"/>
     </row>
@@ -924,22 +924,22 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>-8.998095667000685</v>
+        <v>-2.305603746454738</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>-3.56821801762081</v>
+        <v>-5.419696497145102</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>3.31559019523541</v>
+        <v>5.689822838627459</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>-0.339923960557466</v>
+        <v>-0.1140029749798258</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>-0.2588578189087622</v>
+        <v>-0.3848998607732487</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.1577505590721165</v>
+        <v>0.2882949115705843</v>
       </c>
     </row>
     <row r="17">
@@ -950,22 +950,22 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>-27.29317106577904</v>
+        <v>-17.93312095881051</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>-16.59218903570797</v>
+        <v>-18.11755744172816</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>-14.2053328364618</v>
+        <v>-11.43748807458445</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>-0.7804501305332222</v>
+        <v>-0.6684641395400001</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>-0.8132511264561941</v>
+        <v>-0.8336830980655695</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>-0.4835962523817675</v>
+        <v>-0.4371953827589281</v>
       </c>
     </row>
     <row r="18">
@@ -976,22 +976,22 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>9.664151951620999</v>
+        <v>12.24125492808636</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>8.853440096935792</v>
+        <v>4.816288406519185</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>22.54006669530492</v>
+        <v>20.95868054666738</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>0.6429313147430641</v>
+        <v>0.976466979788822</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>1.625432448169214</v>
+        <v>1.009585518433374</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>1.949190881998455</v>
+        <v>1.675462318938717</v>
       </c>
     </row>
     <row r="19">
@@ -1006,22 +1006,22 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>-3.935366896930343</v>
+        <v>-1.914979362580036</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>-16.34728789859869</v>
+        <v>-18.21048633759427</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>-18.78254175898835</v>
+        <v>-13.90114185464273</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>-0.2318537197774255</v>
+        <v>-0.113880181480265</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>-0.6439837562365479</v>
+        <v>-0.6753505575996522</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>-0.8345650573044178</v>
+        <v>-0.6794449038516228</v>
       </c>
     </row>
     <row r="20">
@@ -1032,19 +1032,19 @@
         </is>
       </c>
       <c r="C20" s="5" t="n">
-        <v>-16.43405182270293</v>
+        <v>-14.12137659555377</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>-29.40888116450314</v>
+        <v>-31.24733824900746</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>-34.67862147113122</v>
+        <v>-29.8089864628276</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>-0.6933376707001725</v>
+        <v>-0.6111226437034886</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>-0.8833649697291323</v>
+        <v>-0.8718615688173529</v>
       </c>
       <c r="H20" s="6" t="n">
         <v>-1</v>
@@ -1058,22 +1058,22 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>8.064442947998215</v>
+        <v>11.61925270633956</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>-2.811443882866079</v>
+        <v>-5.723487872794101</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>-2.668459718659377</v>
+        <v>1.552385698408728</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>0.8778050945424346</v>
+        <v>1.042510624441394</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>-0.1028432128574257</v>
+        <v>-0.1902893439310883</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>0.5793346581760221</v>
+        <v>0.5230622030984712</v>
       </c>
     </row>
     <row r="22">
@@ -1088,22 +1088,22 @@
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>-9.19805969453992</v>
+        <v>-5.796979865884996</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>-2.730004974399967</v>
+        <v>-0.8133210760252405</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>-10.82842476373309</v>
+        <v>-9.342946153454108</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>-0.3649277575931894</v>
+        <v>-0.2582625934543319</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>-0.1866798193466331</v>
+        <v>-0.06347432773100406</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>-0.3701386414010073</v>
+        <v>-0.331070196126461</v>
       </c>
     </row>
     <row r="23">
@@ -1114,22 +1114,22 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>-18.73419702349555</v>
+        <v>-13.88490376454596</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>-10.396231330617</v>
+        <v>-7.960031189119837</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>-25.91293482209681</v>
+        <v>-22.70979544854268</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>-0.6211217377033321</v>
+        <v>-0.524044581308307</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>-0.546968183208279</v>
+        <v>-0.483426496658985</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>-0.7010545689016542</v>
+        <v>-0.6592210351505666</v>
       </c>
     </row>
     <row r="24">
@@ -1140,22 +1140,22 @@
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>0.223260343800648</v>
+        <v>3.442377487110811</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>4.799255029702823</v>
+        <v>5.9820169077896</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>3.395698213296947</v>
+        <v>4.798280406279598</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>0.03966710373798048</v>
+        <v>0.2090517454388109</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>0.4620859419026168</v>
+        <v>0.6518729119834554</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>0.1849708182332697</v>
+        <v>0.272626680195759</v>
       </c>
     </row>
     <row r="25">
@@ -1170,22 +1170,22 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>-3.78045120655307</v>
+        <v>-5.064926100666928</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>-3.229182386686885</v>
+        <v>-2.749288397337763</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>-9.914836707730112</v>
+        <v>-9.918648315736334</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>-0.1033673437921766</v>
+        <v>-0.1485695396708563</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>-0.1748735449935224</v>
+        <v>-0.1596277845241492</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>-0.699005281324902</v>
+        <v>-0.7163205188148796</v>
       </c>
     </row>
     <row r="26">
@@ -1196,22 +1196,22 @@
         </is>
       </c>
       <c r="C26" s="5" t="n">
-        <v>-14.148455765934</v>
+        <v>-14.08877198094727</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>-10.4370494036487</v>
+        <v>-9.612299417885907</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>-18.8736018772094</v>
+        <v>-18.42522401208667</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>-0.3338994372966857</v>
+        <v>-0.361948577354003</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>-0.4722118659359292</v>
+        <v>-0.4759272015958777</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>-0.913231069626546</v>
+        <v>-0.9113888558599825</v>
       </c>
     </row>
     <row r="27">
@@ -1222,22 +1222,22 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>6.841250858933646</v>
+        <v>3.658240113762473</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>5.016949129590428</v>
+        <v>4.103686165528098</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>-3.138526778787488</v>
+        <v>-3.518646678655309</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>0.2301811043325115</v>
+        <v>0.1413862235704152</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>0.3645865768911571</v>
+        <v>0.3553253486063612</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>-0.1979562175789493</v>
+        <v>-0.285099690769295</v>
       </c>
     </row>
     <row r="28">
@@ -1252,22 +1252,22 @@
         </is>
       </c>
       <c r="C28" s="5" t="n">
-        <v>-6.259348845375815</v>
+        <v>-4.826569291150654</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>-7.554169948985562</v>
+        <v>-7.441287865984539</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>-8.257425787586413</v>
+        <v>-7.284750954182556</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>-0.2229787193260811</v>
+        <v>-0.1867183351947454</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>-0.3517942825767651</v>
+        <v>-0.3671751801100362</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>-0.4137454233637529</v>
+        <v>-0.3801287632498864</v>
       </c>
     </row>
     <row r="29">
@@ -1278,22 +1278,22 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>-10.8824037842611</v>
+        <v>-8.578672224337689</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>-11.27018647300211</v>
+        <v>-10.92596402798728</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>-13.45718379368242</v>
+        <v>-12.46873446246795</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>-0.3544774762113587</v>
+        <v>-0.3111706882688562</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>-0.4782752908541811</v>
+        <v>-0.4941096014565154</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>-0.5792645635859314</v>
+        <v>-0.5729224617793113</v>
       </c>
     </row>
     <row r="30">
@@ -1304,22 +1304,22 @@
         </is>
       </c>
       <c r="C30" s="5" t="n">
-        <v>-1.641347644044664</v>
+        <v>-0.7260693950372041</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>-3.917953806249336</v>
+        <v>-3.97515238905609</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>-2.891569949231347</v>
+        <v>-2.422193359406978</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>-0.06625092445245986</v>
+        <v>-0.0301810895391834</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>-0.1927289360695908</v>
+        <v>-0.2161469352470453</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>-0.157786873515665</v>
+        <v>-0.1301259969326855</v>
       </c>
     </row>
     <row r="31">
